--- a/src/main/java/ExcelDriven/TestData.xlsx
+++ b/src/main/java/ExcelDriven/TestData.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Document-Local/Documents/Development_Local/Selenium_Java_TestNG_CICD/src/main/java/ExcelDriven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{055229A0-2439-8144-954B-10DD6EE4A293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA2C385-1D6F-B446-A19C-2BF0529F75A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21240" yWindow="-17560" windowWidth="21100" windowHeight="14140" xr2:uid="{8BE74E13-B701-EE47-BE6E-DB9584CA421A}"/>
+    <workbookView xWindow="-27140" yWindow="-19460" windowWidth="21100" windowHeight="14140" xr2:uid="{8BE74E13-B701-EE47-BE6E-DB9584CA421A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="testData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sample" sheetId="2" r:id="rId2"/>
+    <sheet name="Demo" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -432,7 +434,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F737311-6D00-5044-894B-86F72F135434}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="6.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -471,4 +477,22 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{400BA1E6-1239-F948-B36E-02A3BA1864E8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2ED03C3-752C-0846-86AA-DCC17EC42410}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/java/ExcelDriven/TestData.xlsx
+++ b/src/main/java/ExcelDriven/TestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Document-Local/Documents/Development_Local/Selenium_Java_TestNG_CICD/src/main/java/ExcelDriven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA2C385-1D6F-B446-A19C-2BF0529F75A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5F6509-DC90-544D-8E20-3F2ACB56465A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27140" yWindow="-19460" windowWidth="21100" windowHeight="14140" xr2:uid="{8BE74E13-B701-EE47-BE6E-DB9584CA421A}"/>
+    <workbookView xWindow="-26460" yWindow="-26720" windowWidth="21100" windowHeight="14140" xr2:uid="{8BE74E13-B701-EE47-BE6E-DB9584CA421A}"/>
   </bookViews>
   <sheets>
     <sheet name="testData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>TestCases</t>
   </si>
@@ -62,6 +62,39 @@
   </si>
   <si>
     <t>Delete Profile</t>
+  </si>
+  <si>
+    <t>QQ</t>
+  </si>
+  <si>
+    <t>WW</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>DD</t>
+  </si>
+  <si>
+    <t>ZZ</t>
+  </si>
+  <si>
+    <t>XX</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>QWE</t>
+  </si>
+  <si>
+    <t>WER</t>
   </si>
 </sst>
 </file>
@@ -458,20 +491,56 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/ExcelDriven/TestData.xlsx
+++ b/src/main/java/ExcelDriven/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Document-Local/Documents/Development_Local/Selenium_Java_TestNG_CICD/src/main/java/ExcelDriven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5F6509-DC90-544D-8E20-3F2ACB56465A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5CFA4B-8A38-6B49-B77C-700E4BAE0D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26460" yWindow="-26720" windowWidth="21100" windowHeight="14140" xr2:uid="{8BE74E13-B701-EE47-BE6E-DB9584CA421A}"/>
+    <workbookView xWindow="29160" yWindow="-20120" windowWidth="21100" windowHeight="14140" xr2:uid="{8BE74E13-B701-EE47-BE6E-DB9584CA421A}"/>
   </bookViews>
   <sheets>
     <sheet name="testData" sheetId="1" r:id="rId1"/>

--- a/src/main/java/ExcelDriven/TestData.xlsx
+++ b/src/main/java/ExcelDriven/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Document-Local/Documents/Development_Local/Selenium_Java_TestNG_CICD/src/main/java/ExcelDriven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5CFA4B-8A38-6B49-B77C-700E4BAE0D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362E2D39-8951-9E47-87DD-5A9B0EDAAF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29160" yWindow="-20120" windowWidth="21100" windowHeight="14140" xr2:uid="{8BE74E13-B701-EE47-BE6E-DB9584CA421A}"/>
+    <workbookView xWindow="-20" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{8BE74E13-B701-EE47-BE6E-DB9584CA421A}"/>
   </bookViews>
   <sheets>
     <sheet name="testData" sheetId="1" r:id="rId1"/>

--- a/src/main/java/ExcelDriven/TestData.xlsx
+++ b/src/main/java/ExcelDriven/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Document-Local/Documents/Development_Local/Selenium_Java_TestNG_CICD/src/main/java/ExcelDriven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362E2D39-8951-9E47-87DD-5A9B0EDAAF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141E7FEB-F332-BD42-B4CC-99F29DA038E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{8BE74E13-B701-EE47-BE6E-DB9584CA421A}"/>
   </bookViews>

--- a/src/main/java/ExcelDriven/TestData.xlsx
+++ b/src/main/java/ExcelDriven/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Document-Local/Documents/Development_Local/Selenium_Java_TestNG_CICD/src/main/java/ExcelDriven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141E7FEB-F332-BD42-B4CC-99F29DA038E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FF106D-BB40-A440-A822-2A84829AFDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{8BE74E13-B701-EE47-BE6E-DB9584CA421A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{8BE74E13-B701-EE47-BE6E-DB9584CA421A}"/>
   </bookViews>
   <sheets>
     <sheet name="testData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>TestCases</t>
   </si>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t>ZZ</t>
-  </si>
-  <si>
-    <t>XX</t>
   </si>
   <si>
     <t>CC</t>
@@ -522,11 +519,11 @@
       <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -534,13 +531,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
